--- a/RandomForest/RandomForest Notes.xlsx
+++ b/RandomForest/RandomForest Notes.xlsx
@@ -5,17 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattamor/MachineLearningProject_Group1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d20b6f89a61f61e/School/ECON 6378 - Machines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8601BE-7597-7249-8867-3B31BE17E9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8F7D1D9-FE54-4A4A-8F33-9757708DE320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="1020" windowWidth="25040" windowHeight="14100" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
+    <workbookView xWindow="460" yWindow="1020" windowWidth="25040" windowHeight="14100" activeTab="5" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tree" sheetId="3" r:id="rId1"/>
+    <sheet name="RandomForest" sheetId="1" r:id="rId2"/>
+    <sheet name="xGboost" sheetId="5" r:id="rId3"/>
+    <sheet name="CatBoost" sheetId="6" r:id="rId4"/>
+    <sheet name="Lasso" sheetId="4" r:id="rId5"/>
+    <sheet name="Logit" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>class.error</t>
   </si>
@@ -66,14 +71,40 @@
   </si>
   <si>
     <t>Total Error</t>
+  </si>
+  <si>
+    <t>Total error</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Check Test</t>
+  </si>
+  <si>
+    <t>Check Test - is_older_american</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test - </t>
+  </si>
+  <si>
+    <t>False Neg</t>
+  </si>
+  <si>
+    <t>False Pos.</t>
+  </si>
+  <si>
+    <t>Test -  Non older americans</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="168" formatCode="0.00000000000000%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -183,29 +214,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,17 +575,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D91954-EDEB-F848-A538-5BC73681F1AA}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>8534</v>
+      </c>
+      <c r="C2">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>558</v>
+      </c>
+      <c r="C3">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
+        <f>B3/SUM(B2:B3)</f>
+        <v>6.137263528376595E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <f>C2/SUM(C2:C3)</f>
+        <v>0.63136770608212411</v>
+      </c>
+      <c r="D4" s="1">
+        <f>SUM(C2,B3)/SUM(B2:C3)</f>
+        <v>0.2110939907550077</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <f>1-D4</f>
+        <v>0.78890600924499232</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>21174</v>
+      </c>
+      <c r="C10">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1612</v>
+      </c>
+      <c r="C11">
+        <v>3365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="1">
+        <f>B11/SUM(B10:B11)</f>
+        <v>7.0745194417624863E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <f>C10/SUM(C10:C11)</f>
+        <v>0.59379526798647997</v>
+      </c>
+      <c r="D12" s="1">
+        <f>SUM(C10,B11)/SUM(B10:C11)</f>
+        <v>0.21020276794335371</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="16">
+        <f>(C19-C12)/C19</f>
+        <v>0.1641686173451179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D13" s="1">
+        <f>1-D12</f>
+        <v>0.78979723205664631</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>847</v>
+      </c>
+      <c r="C17">
+        <v>184</v>
+      </c>
+      <c r="E17">
+        <f>SUM(B17:C18)</f>
+        <v>1158</v>
+      </c>
+      <c r="F17">
+        <f>SUM(B17:C17)</f>
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>52</v>
+      </c>
+      <c r="C18">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="1">
+        <f>B18/SUM(B17:B18)</f>
+        <v>5.7842046718576193E-2</v>
+      </c>
+      <c r="C19" s="1">
+        <f>C17/SUM(C17:C18)</f>
+        <v>0.71042471042471045</v>
+      </c>
+      <c r="D19" s="1">
+        <f>SUM(C17,B18)/SUM(B17:C18)</f>
+        <v>0.20379965457685664</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D20" s="1">
+        <f>1-D19</f>
+        <v>0.79620034542314333</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A15:E15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D53ACE2-2150-064E-B5C8-0AB1C12F8644}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2">
@@ -573,7 +823,7 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>C3/SUM(B3:C3)</f>
         <v>0</v>
       </c>
@@ -588,24 +838,24 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>B4/SUM(B4:C4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>(C3+B4)/SUM(B3:C4)</f>
         <v>0.26390000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="A7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8">
@@ -628,7 +878,7 @@
       <c r="C9">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>6.7925549999999998E-4</v>
       </c>
     </row>
@@ -642,23 +892,23 @@
       <c r="C10">
         <v>52</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>0.98029556650000005</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>(C9+B10)/SUM(B9:C10)</f>
         <v>0.25919999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
@@ -669,70 +919,76 @@
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4">
         <v>1390</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="5">
         <v>475</v>
       </c>
-      <c r="E17" s="2">
-        <f>D17/SUM(C17:D17)</f>
-        <v>0.2546916890080429</v>
-      </c>
-      <c r="F17" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="A18" s="12"/>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5">
         <v>86</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="4">
         <v>49</v>
       </c>
-      <c r="E18" s="2">
-        <f>C18/SUM(C18:D18)</f>
-        <v>0.63703703703703707</v>
-      </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E19" s="2">
+      <c r="C19" s="1">
+        <f>D17/SUM(C17:C18)</f>
+        <v>0.32181571815718157</v>
+      </c>
+      <c r="D19" s="1">
+        <f>C18/SUM(D17:D18)</f>
+        <v>0.16412213740458015</v>
+      </c>
+      <c r="E19" s="1">
         <f>(C18+D17)/SUM(C17:D18)</f>
         <v>0.28050000000000003</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="14">
+        <f>1-E19</f>
+        <v>0.71950000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -746,4 +1002,368 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8643C6-638B-2444-A0E5-8D9E62FB83B8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DDB164-21FC-2749-81C6-202A679DB7EF}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>42603</v>
+      </c>
+      <c r="C2">
+        <v>9747</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2857</v>
+      </c>
+      <c r="C3">
+        <v>6449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
+        <f>B3/SUM(B2:B3)</f>
+        <v>6.2846458424988996E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <f>C2/SUM(C2:C3)</f>
+        <v>0.60181526302790811</v>
+      </c>
+      <c r="D4" s="1">
+        <f>SUM(C2,B3)/SUM(B2:C3)</f>
+        <v>0.20442454911119762</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <f>1-D4</f>
+        <v>0.79557545088880244</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB706E7A-24EB-554D-8AE4-2B2BE8923685}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23EBDEE-21FC-854D-930A-6DB3F5A7C024}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>21216</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1570</v>
+      </c>
+      <c r="F4">
+        <f>SUM(C4:D5)</f>
+        <v>31070</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>5137</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C6" s="1">
+        <f>C5/SUM(C4:C5)</f>
+        <v>0.19493036845899897</v>
+      </c>
+      <c r="D6" s="1">
+        <f>D4/SUM(D4:D5)</f>
+        <v>0.33283866864532541</v>
+      </c>
+      <c r="E6" s="1">
+        <f>(C5+D4)/SUM(C4:D5)</f>
+        <v>0.21586739620212422</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="14">
+        <f>1-E6</f>
+        <v>0.78413260379787575</v>
+      </c>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>849</v>
+      </c>
+      <c r="D12" s="5">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <f>SUM(C12:D13)</f>
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>191</v>
+      </c>
+      <c r="D13" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C14" s="1">
+        <f>C13/SUM(C12:C13)</f>
+        <v>0.18365384615384617</v>
+      </c>
+      <c r="D14" s="1">
+        <f>D12/SUM(D12:D13)</f>
+        <v>0.42372881355932202</v>
+      </c>
+      <c r="E14" s="1">
+        <f>(C13+D12)/SUM(C12:D13)</f>
+        <v>0.2081174438687392</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="14">
+        <f>1-E14</f>
+        <v>0.7918825561312608</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>20367</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1520</v>
+      </c>
+      <c r="F20">
+        <f>SUM(C20:D21)</f>
+        <v>29912</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4946</v>
+      </c>
+      <c r="D21" s="15">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C22" s="1">
+        <f>C21/SUM(C20:C21)</f>
+        <v>0.19539367123612372</v>
+      </c>
+      <c r="D22" s="1">
+        <f>D20/SUM(D20:D21)</f>
+        <v>0.33050663187649487</v>
+      </c>
+      <c r="E22" s="1">
+        <f>(C21+D20)/SUM(C20:D21)</f>
+        <v>0.21616742444503878</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="14">
+        <f>1-E22</f>
+        <v>0.78383257555496122</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:A13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RandomForest/RandomForest Notes.xlsx
+++ b/RandomForest/RandomForest Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattamor/MachineLearningProject_Group1/RandomForest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B84F801-212C-7B4C-9ACB-AAE95714B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B70FBE2-3244-254A-A4BB-75874C5A0CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="1020" windowWidth="25040" windowHeight="14100" activeTab="5" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
+    <workbookView xWindow="440" yWindow="1020" windowWidth="35860" windowHeight="17480" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
   </bookViews>
   <sheets>
     <sheet name="Tree" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="10">
   <si>
     <t xml:space="preserve">          Reference</t>
   </si>
@@ -77,9 +77,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="166" formatCode="0.00000000000000%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
@@ -190,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -202,7 +201,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -213,9 +211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,47 +547,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D91954-EDEB-F848-A538-5BC73681F1AA}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="A1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>21174</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4919</v>
+      </c>
+      <c r="F4">
+        <f>SUM(C4:D5)</f>
+        <v>31070</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1612</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3365</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D6" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C6" s="1">
+        <f>C5/SUM(C4:C5)</f>
+        <v>7.0745194417624863E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <f>D4/SUM(D4:D5)</f>
+        <v>0.59379526798647997</v>
+      </c>
+      <c r="E6" s="1">
+        <f>(C5+D4)/SUM(C4:D5)</f>
+        <v>0.21020276794335371</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="15">
+        <f>1-E6</f>
+        <v>0.78979723205664631</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>184</v>
+      </c>
+      <c r="F12">
+        <f>SUM(C12:D13)</f>
+        <v>1158</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D13" s="1"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C14" s="1">
+        <f>C13/SUM(C12:C13)</f>
+        <v>5.7842046718576193E-2</v>
+      </c>
+      <c r="D14" s="1">
+        <f>D12/SUM(D12:D13)</f>
+        <v>0.71042471042471045</v>
+      </c>
+      <c r="E14" s="1">
+        <f>(C13+D12)/SUM(C12:D13)</f>
+        <v>0.20379965457685664</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="9">
+        <f>1-E14</f>
+        <v>0.79620034542314333</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <f>SUM(C12:C13)</f>
+        <v>899</v>
+      </c>
+      <c r="D17">
+        <f>SUM(D12:D13)</f>
+        <v>259</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
+  <mergeCells count="6">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -606,20 +755,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
@@ -632,7 +781,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
@@ -650,7 +799,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -689,23 +838,23 @@
         <f>1-E6</f>
         <v>0.77882201480527846</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -718,7 +867,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2">
@@ -736,7 +885,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2">
         <v>1</v>
       </c>
@@ -778,12 +927,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -795,20 +944,20 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
@@ -821,7 +970,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
@@ -839,7 +988,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -880,20 +1029,20 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -906,7 +1055,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2">
@@ -924,7 +1073,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2">
         <v>1</v>
       </c>
@@ -966,12 +1115,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -983,20 +1132,20 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
@@ -1009,7 +1158,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
@@ -1027,7 +1176,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1068,20 +1217,20 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -1094,7 +1243,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2">
@@ -1112,7 +1261,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2">
         <v>1</v>
       </c>
@@ -1154,12 +1303,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1171,20 +1320,20 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
@@ -1197,7 +1346,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
@@ -1215,7 +1364,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1256,20 +1405,20 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -1282,47 +1431,47 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2">
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>20367</v>
+        <v>850</v>
       </c>
       <c r="D12" s="4">
-        <v>1520</v>
+        <v>197</v>
       </c>
       <c r="F12">
         <f>SUM(C12:D13)</f>
-        <v>29912</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="4">
-        <v>4946</v>
+        <v>49</v>
       </c>
       <c r="D13" s="10">
-        <v>3079</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C14" s="1">
         <f>C13/SUM(C12:C13)</f>
-        <v>0.19539367123612372</v>
+        <v>5.4505005561735265E-2</v>
       </c>
       <c r="D14" s="1">
         <f>D12/SUM(D12:D13)</f>
-        <v>0.33050663187649487</v>
+        <v>0.76061776061776065</v>
       </c>
       <c r="E14" s="1">
         <f>(C13+D12)/SUM(C12:D13)</f>
-        <v>0.21616742444503878</v>
+        <v>0.21243523316062177</v>
       </c>
       <c r="F14" t="s">
         <v>2</v>
@@ -1337,17 +1486,17 @@
       </c>
       <c r="E15" s="9">
         <f>1-E14</f>
-        <v>0.78383257555496122</v>
+        <v>0.78756476683937826</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1362,20 +1511,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
@@ -1388,7 +1537,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
@@ -1406,7 +1555,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1445,23 +1594,23 @@
         <f>1-E6</f>
         <v>0.7815577727711619</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -1474,7 +1623,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2">
@@ -1492,7 +1641,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="2">
         <v>1</v>
       </c>
@@ -1544,12 +1693,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
